--- a/input/requirements/Procedure.xlsx
+++ b/input/requirements/Procedure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahenket/Development/GitHub/Nictiz/GBB-IG/input/requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TessavanAlphen\Projects\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2BF520-300F-7849-93DE-28B406CAEEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E763DAFF-1EFF-401A-84AC-F527979C6F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="-35240" windowWidth="44340" windowHeight="30740" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -216,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="401">
   <si>
     <t>Veld</t>
   </si>
@@ -245,15 +245,9 @@
     <t>Representatie</t>
   </si>
   <si>
-    <t>Zie comment.</t>
-  </si>
-  <si>
     <t>Alias(sen)</t>
   </si>
   <si>
-    <t>Behandeling (dekt maar een deel van het concept verrichting)</t>
-  </si>
-  <si>
     <t>Juist gebruik</t>
   </si>
   <si>
@@ -263,18 +257,12 @@
     <t>Onjuist gebruik</t>
   </si>
   <si>
-    <t>Het concept is niet bedoeld voor het vastleggen van verpleegkundige verrichtingen, administratieve verrichtingen en dat wat niet een verrichting is. Hiervoor zijn nog geen generieke bouwblokken ontwikkeld.</t>
-  </si>
-  <si>
     <t> Niet bedoeld voor de aanvraag van een verrichting. Niet bedoeld voor vaccinaties. Niet bedoeld voor het vastleggen van zwangerschapsverrichtingseigenschappen, hiervoor zijn gespecialiseerde concepten, als subconcept van dit concept. Niet bedoeld voor gewenste maar nog niet geplande verrichtingen, dit hoort eerder in een zorgplan.</t>
   </si>
   <si>
     <t>Referenties</t>
   </si>
   <si>
-    <t>Zibs, Geboortezorg, JGZ, Acute zorg, Huisartsenzorg, BgZ-MSZ, eOverdracht</t>
-  </si>
-  <si>
     <t>zibVerrichting(2024) https://zibs.nl/wiki/Verrichting-v6.0(2024NL) zibVerpleegkundigeInterventie(2024) https://zibs.nl/wiki/VerpleegkundigeInterventie-v5.0(2024NL)  XtEHRProcedure(v0.2.1)  openEHRProcedure(v1.4.10) FHIRProcedure(R5)</t>
   </si>
   <si>
@@ -317,9 +305,6 @@
     <t>Een exacte datum en tijd, een datum, en een vage datum zijn allemaal toegestaan</t>
   </si>
   <si>
-    <t>Alleen bedoeld voor uitgevoerde verrichtingen. Niet te gebruiken als startdatum of einddatum zijn ingevuld.</t>
-  </si>
-  <si>
     <t>Zie hieronder</t>
   </si>
   <si>
@@ -335,9 +320,6 @@
     <t>Datum en tijd van uitgevoerde verrichting</t>
   </si>
   <si>
-    <t>Zie hierboven</t>
-  </si>
-  <si>
     <t>1.1.1</t>
   </si>
   <si>
@@ -365,9 +347,6 @@
     <t>Een exacte datum en tijd, een datum, en een vage datum zijn allemaal toegestaan voor zowel het begin als het eind</t>
   </si>
   <si>
-    <t>Alleen relevant uitgevoerde verrichtingen. Niet te gebruiken als er alleen een datum/tijd van uitvoering gewenst is.</t>
-  </si>
-  <si>
     <t>1.1.3</t>
   </si>
   <si>
@@ -380,12 +359,6 @@
     <t>De einddatum (en eventueel eindtijd) van de verrichting wanneer het om anamnistische registraties gaat (bv. "patiënt wat tot twee jaar geleden onder behandeling").</t>
   </si>
   <si>
-    <t>Dit zal doorgaans een datum zonder tijd of een vage daum zijn.</t>
-  </si>
-  <si>
-    <t>Alleen aanwezig bij afgeronde verrichtingen. Niet te gebruiken als er alleen een datum/tijd van uitvoering gewenst is of als er een periode is.</t>
-  </si>
-  <si>
     <t>zibVerrichting(2024)</t>
   </si>
   <si>
@@ -404,9 +377,6 @@
     <t>Doorgaans aanwezig bij gestarte verrichtingen</t>
   </si>
   <si>
-    <t>Hier moeten we wel aan denken bij elke informatiebehoefte maar hebben we nu geen bron voor</t>
-  </si>
-  <si>
     <t>1.3</t>
   </si>
   <si>
@@ -422,9 +392,6 @@
     <t>Een exacte datum en tijd of alleen een datum</t>
   </si>
   <si>
-    <t>Alleen relevant voor geplande verrichtingen</t>
-  </si>
-  <si>
     <t>1.4</t>
   </si>
   <si>
@@ -491,9 +458,6 @@
     <t>Er is behoefte om het minimum interval aan te geven</t>
   </si>
   <si>
-    <t>Zie hierboven, wanneer er een minimum interval is</t>
-  </si>
-  <si>
     <t>2.2</t>
   </si>
   <si>
@@ -503,9 +467,6 @@
     <t>Er is behoefte om het gewenste interval aan te geven</t>
   </si>
   <si>
-    <t>Zie hierboven, wanneer er een gewenste interval is</t>
-  </si>
-  <si>
     <t>2.3</t>
   </si>
   <si>
@@ -515,9 +476,6 @@
     <t>Er is behoefte om het maximum interval aan te geven</t>
   </si>
   <si>
-    <t>Zie hierboven, wanneer er een maximum interval is</t>
-  </si>
-  <si>
     <t>De persoon of personen die de verrichting heeft uitgevoerd of zal uitvoeren.</t>
   </si>
   <si>
@@ -539,9 +497,6 @@
     <t>Is een referentie naar één of meerdere zorgproffesional(s)</t>
   </si>
   <si>
-    <t>Relevant voor geplande, gestarte of uitgevoerde verrichtingen, kan één persoon zijn of meerdere personen</t>
-  </si>
-  <si>
     <t>zibVerrichting(2024), zibVerpleegkundigeInterventie(2024), XtEHRProcedure(v0.2.1)</t>
   </si>
   <si>
@@ -557,9 +512,6 @@
     <t>Is een referentie naar één of meerdere specialismes van zorgverlener(s)</t>
   </si>
   <si>
-    <t>Relevant voor geplande verrichtingen. Niet te gebruiken als ook de volledige zorgverlener bekend is, deze omvat ook het specialisme.</t>
-  </si>
-  <si>
     <t>zibVerrichting(2024) en zibVerpleegkundigeInterventie(2024)</t>
   </si>
   <si>
@@ -575,9 +527,6 @@
     <t>Is een referentie naar patiënt</t>
   </si>
   <si>
-    <t>Relevant voor geplande, gestarte of uitgevoerde verrichtingen. Kan in combinatie met andere uitvoerders zijn.</t>
-  </si>
-  <si>
     <t>zibVerpleegkundigeInterventie(2024)</t>
   </si>
   <si>
@@ -884,9 +833,6 @@
     <t>De fysieke locatie waar de verrichting is, wordt of zal worden uitgevoerd.</t>
   </si>
   <si>
-    <t>Is een refentie naar een locatie</t>
-  </si>
-  <si>
     <t>5.1</t>
   </si>
   <si>
@@ -950,9 +896,6 @@
     <t>7.2</t>
   </si>
   <si>
-    <t>Reason</t>
-  </si>
-  <si>
     <t>Procedure.reasonCode / reasonReference</t>
   </si>
   <si>
@@ -983,10 +926,6 @@
     <t>BgZ 2017(v2.0 beta)</t>
   </si>
   <si>
-    <t xml:space="preserve">RM: ism_transition/current_state
-</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -1002,10 +941,6 @@
     <t>Procedure.Status</t>
   </si>
   <si>
-    <t xml:space="preserve">	
-A code specifying the state of the procedure. Generally, this will be the in-progress or completed state. For example: preparation, in-progress, not-done, on-hold, stopped, completed, entered-in-error, unknown</t>
-  </si>
-  <si>
     <t>Moet gecodeerd zijn</t>
   </si>
   <si>
@@ -1105,9 +1040,6 @@
     <t>Eerstelijnszorg(v.)</t>
   </si>
   <si>
-    <t>Procedure.encounter.episodeofcare</t>
-  </si>
-  <si>
     <t>Zorgepisode</t>
   </si>
   <si>
@@ -1159,18 +1091,12 @@
     <t>Referentie naar medisch hulpmiddel</t>
   </si>
   <si>
-    <t>Relevant voor gestarte en uitgevoerde verrichtingen</t>
-  </si>
-  <si>
     <t>XTEHRProcedure(v0.2.1)</t>
   </si>
   <si>
     <t>outcome</t>
   </si>
   <si>
-    <t>Procedure.outcome</t>
-  </si>
-  <si>
     <t>Uitkomst</t>
   </si>
   <si>
@@ -1180,16 +1106,9 @@
     <t>Kan gecodeerd zijn</t>
   </si>
   <si>
-    <t>Relevant voor uitgevoerde verrichtingen</t>
-  </si>
-  <si>
     <t>complication</t>
   </si>
   <si>
-    <t>procedure.complication
-procedure.complicationdetail</t>
-  </si>
-  <si>
     <t>Complicatie</t>
   </si>
   <si>
@@ -1211,9 +1130,6 @@
     <t>Additionele informatie</t>
   </si>
   <si>
-    <t>Tekst, optioneel, maximaal 1</t>
-  </si>
-  <si>
     <t>Domainresource</t>
   </si>
   <si>
@@ -1229,10 +1145,6 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>Procedure.subject
-Procedure.status</t>
-  </si>
-  <si>
     <t>EHDSProcedure.header</t>
   </si>
   <si>
@@ -1311,23 +1223,231 @@
     <t>Er is op dit moment nog geen input binnengekomen van team Topgun, waardoor het gebruik en de wensen omtrent verrichting niet meegenomen zijn in deze eerste ontwikkelfase.</t>
   </si>
   <si>
-    <t>4.2.1</t>
-  </si>
-  <si>
-    <t>4.2.2</t>
-  </si>
-  <si>
     <t>ART-DECOR-id</t>
   </si>
   <si>
     <t>2.16.840.1.113883.2.4.3.11.60.153.4.28/2026-07-15T00:00:00</t>
+  </si>
+  <si>
+    <t>Voor elke stap in de levenscyclus van het concept GBB Verrichting/Procedure wordt een instantiatie gemaakt. Deze uitwerking in dit document vloeit voort uit de keuze van het basismodel OpenEHR Procedure.</t>
+  </si>
+  <si>
+    <t>Behandeling (dekt maar een deel van het concept verrichting), (verpleegkundige) interventie, therapie, handelingen (in de ambulanceoverdracht AcuteZorg [Handelingen oxygenatie en ventilatie]) .</t>
+  </si>
+  <si>
+    <t>Het concept is niet bedoeld voor het vastleggen van administratieve verrichtingen, anesthesie, beeld onderzoek, lab onderzoek, instructie of onderwijs en dat wat niet een verrichting is. Hiervoor zijn nog geen generieke bouwblokken ontwikkeld.</t>
+  </si>
+  <si>
+    <t>zibVerrichting2024, Geboortezorg, JGZ, Acute zorg, Huisartsenzorg, BgZ-MSZ, eOverdracht, EEHRXf logical model EHDSProcedure 1.0.0, FHIRProcedure R4, OpenEHRProcedure 1.5.1</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>FeederAuditOriginatingSystemItemIds</t>
+  </si>
+  <si>
+    <t>DateAndTimeActionstepPerformed</t>
+  </si>
+  <si>
+    <t>Indication (zelfde informatiebehoefte als 7.1)</t>
+  </si>
+  <si>
+    <t>RM: ism_transition/current_state</t>
+  </si>
+  <si>
+    <t>informationProvider</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>identifier</t>
+  </si>
+  <si>
+    <t>PerformedPeriodStart</t>
+  </si>
+  <si>
+    <t>extension:recorded</t>
+  </si>
+  <si>
+    <t>procedure.complication</t>
+  </si>
+  <si>
+    <t>asserter</t>
+  </si>
+  <si>
+    <t>recorder</t>
+  </si>
+  <si>
+    <t>Identificatienummer</t>
+  </si>
+  <si>
+    <t>header.date</t>
+  </si>
+  <si>
+    <t>Source/bron</t>
+  </si>
+  <si>
+    <t>Author/Auteur</t>
+  </si>
+  <si>
+    <t>Language/Taal</t>
+  </si>
+  <si>
+    <t>Procedure.outcome procedure.complicationdetail</t>
+  </si>
+  <si>
+    <t>Procedure.subject, Procedure.status</t>
+  </si>
+  <si>
+    <t>Identificatienummer voor het object, uniek binnen het betreffende systeem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state. For example: preparation, in-progress, not-done, on-hold, stopped, completed, entered-in-error, unknown</t>
+  </si>
+  <si>
+    <t>EHDS: Date and optionally time of authoring/issuing, openEHR: De datum en het tijdstip waarop deze stap van de actie is uitgevoerd.</t>
+  </si>
+  <si>
+    <t>Dit zal doorgaans een datum zonder tijd of een vage datum zijn.</t>
+  </si>
+  <si>
+    <t>DateTime (tijd optioneel)</t>
+  </si>
+  <si>
+    <t>Verwijzing naar andere uitvoerders</t>
+  </si>
+  <si>
+    <t>Is een referentie naar een locatie</t>
+  </si>
+  <si>
+    <t>Vrije tekst</t>
+  </si>
+  <si>
+    <t>Codeable concept, eg patient / patient proxy</t>
+  </si>
+  <si>
+    <t>Verwijzing naar healthprofessional, organisation, device</t>
+  </si>
+  <si>
+    <t>codeable concept, binding : (preferred): BCP 47</t>
+  </si>
+  <si>
+    <t>0..*</t>
+  </si>
+  <si>
+    <t>0..1</t>
+  </si>
+  <si>
+    <t>Relevant als er een planning gemaakt moet worden waarbij het referentiepunt nog niet is bepaald, wanneer er een minimum interval is</t>
+  </si>
+  <si>
+    <t>Relevant als er een planning gemaakt moet worden waarbij het referentiepunt nog niet is bepaald, wanneer er een gewenste interval is</t>
+  </si>
+  <si>
+    <t>Relevant als er een planning gemaakt moet worden waarbij het referentiepunt nog niet is bepaald, wanneer er een maximum interval is</t>
+  </si>
+  <si>
+    <t>0..1
+Alleen bedoeld voor uitgevoerde verrichtingen. Niet te gebruiken als startdatum of einddatum zijn ingevuld.</t>
+  </si>
+  <si>
+    <t>0..1
+Alleen relevant uitgevoerde verrichtingen. Niet te gebruiken als er alleen een datum/tijd van uitvoering gewenst is.</t>
+  </si>
+  <si>
+    <t>0..1
+Alleen aanwezig bij afgeronde verrichtingen. Niet te gebruiken als er alleen een datum/tijd van uitvoering gewenst is of als er een periode is.</t>
+  </si>
+  <si>
+    <t>0..1
+Hier moeten we wel aan denken bij elke informatiebehoefte maar hebben we nu geen bron voor</t>
+  </si>
+  <si>
+    <t>0..1
+Alleen relevant voor geplande verrichtingen</t>
+  </si>
+  <si>
+    <t>1..1
+Altijd aanwezig</t>
+  </si>
+  <si>
+    <t>0..*
+Relevant voor geplande, gestarte of uitgevoerde verrichtingen, kan één persoon zijn of meerdere personen</t>
+  </si>
+  <si>
+    <t>0..*
+Relevant voor geplande verrichtingen. Niet te gebruiken als ook de volledige zorgverlener bekend is, deze omvat ook het specialisme.</t>
+  </si>
+  <si>
+    <t>0..*
+Relevant voor geplande, gestarte of uitgevoerde verrichtingen. Kan in combinatie met andere uitvoerders zijn.</t>
+  </si>
+  <si>
+    <t>1..1
+Relevant voor geplande, gestarte en uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..1
+Relevant voor geplande, gestarte of uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..*
+Relevant voor geplande, gestarte of uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..* 
+Relevant voor geplande, gestarte of uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..1 
+Relevant voor geplande, gestarte en uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>1..1
+Verplicht, max 1 (Altijd aanwezig)</t>
+  </si>
+  <si>
+    <t>1..1 
+Altijd aanwezig</t>
+  </si>
+  <si>
+    <t>0..*
+Relevant voor geplande, gestarte en uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..*
+Relevant voor gestarte en uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..1
+Relevant voor uitgevoerde verrichtingen</t>
+  </si>
+  <si>
+    <t>0..*
+Optioneel (Relevant voor gestarte en uitgevoerde verrichtingen)</t>
+  </si>
+  <si>
+    <t>0..1
+Optioneel en maximaal 1 (Relevant voor geplande, gestarte en uitgevoerde verrichtingen)</t>
+  </si>
+  <si>
+    <t>1..1
+Verplicht</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1360,13 +1480,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9"/>
+      <color rgb="FF4EA72E"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1377,6 +1505,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1A983"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1402,20 +1542,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1423,19 +1553,31 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2555,12 +2697,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="218.5" customWidth="1"/>
+    <col min="1" max="1" width="218.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
     </row>
   </sheetData>
@@ -2572,18 +2714,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="191" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="190.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="59.6640625" customWidth="1"/>
-    <col min="3" max="3" width="58.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="99.83203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="58.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="99.77734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="191" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="190.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2591,82 +2733,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="10" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B7" s="10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B8" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B9" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B10" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="64" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -2678,1765 +2820,1894 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:K75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K77"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="4" customWidth="1"/>
+    <col min="1" max="2" width="22.44140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="4" customWidth="1"/>
     <col min="4" max="4" width="17" style="4" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="68.5" customWidth="1"/>
-    <col min="7" max="7" width="52.1640625" customWidth="1"/>
+    <col min="6" max="6" width="68.44140625" customWidth="1"/>
+    <col min="7" max="7" width="52.109375" customWidth="1"/>
     <col min="8" max="9" width="48.6640625" customWidth="1"/>
-    <col min="10" max="10" width="34.5" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
     <col min="11" max="11" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="F2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H4" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="D5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="E5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="F5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
+      <c r="F6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="G6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="3" t="s">
+    </row>
+    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="D7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="F7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="H13" t="s">
+        <v>375</v>
+      </c>
+      <c r="J13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>2</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>376</v>
+      </c>
+      <c r="J15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s">
+        <v>378</v>
+      </c>
+      <c r="J17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>3</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="J18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="3" t="s">
+    </row>
+    <row r="22" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>4</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="J44" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="3" t="s">
+      <c r="C45" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="J45" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="11"/>
+      <c r="B46" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" s="5" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>5</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>6</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
+        <v>7</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="J51" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J52" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="11">
+        <v>8</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>9</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G55" s="13">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
+        <v>117</v>
+      </c>
+      <c r="J55" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="J56" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" t="s">
+    </row>
+    <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J57" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
+        <v>10</v>
+      </c>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="H59" t="s">
         <v>117</v>
       </c>
-      <c r="G19" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" t="s">
-        <v>123</v>
-      </c>
-      <c r="G20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" t="s">
-        <v>119</v>
-      </c>
-      <c r="J20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
-        <v>4</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F26" t="s">
-        <v>147</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F29" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" t="s">
-        <v>162</v>
-      </c>
-      <c r="F30" t="s">
-        <v>163</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" t="s">
-        <v>166</v>
-      </c>
-      <c r="F31" t="s">
-        <v>167</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" t="s">
-        <v>170</v>
-      </c>
-      <c r="F32" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F33" t="s">
-        <v>175</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" t="s">
-        <v>178</v>
-      </c>
-      <c r="F34" t="s">
-        <v>179</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" t="s">
-        <v>186</v>
-      </c>
-      <c r="F36" t="s">
-        <v>187</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" t="s">
-        <v>190</v>
-      </c>
-      <c r="F37" t="s">
-        <v>191</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" t="s">
-        <v>194</v>
-      </c>
-      <c r="F38" t="s">
-        <v>195</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" t="s">
-        <v>198</v>
-      </c>
-      <c r="F39" t="s">
-        <v>199</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H39" s="3" t="s">
+      <c r="J59" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J60" t="s">
         <v>200</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" t="s">
-        <v>202</v>
-      </c>
-      <c r="F40" t="s">
-        <v>203</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" t="s">
-        <v>207</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" t="s">
-        <v>130</v>
-      </c>
-      <c r="F43" t="s">
-        <v>212</v>
-      </c>
-      <c r="G43" t="s">
-        <v>213</v>
-      </c>
-      <c r="H43" t="s">
-        <v>80</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" t="s">
-        <v>214</v>
-      </c>
-      <c r="F44" t="s">
-        <v>215</v>
-      </c>
-      <c r="G44" t="s">
-        <v>216</v>
-      </c>
-      <c r="H44" t="s">
-        <v>80</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J44" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="6">
-        <v>5</v>
-      </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E46" t="s">
-        <v>224</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E47" t="s">
-        <v>228</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A48" s="6">
-        <v>6</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
-        <v>7</v>
-      </c>
-      <c r="E49" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" t="s">
-        <v>240</v>
-      </c>
-      <c r="F50" t="s">
-        <v>241</v>
-      </c>
-      <c r="G50" t="s">
-        <v>242</v>
-      </c>
-      <c r="H50" t="s">
-        <v>128</v>
-      </c>
-      <c r="J50" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="E51" t="s">
-        <v>246</v>
-      </c>
-      <c r="F51" t="s">
-        <v>247</v>
-      </c>
-      <c r="G51" t="s">
-        <v>248</v>
-      </c>
-      <c r="H51" t="s">
-        <v>128</v>
-      </c>
-      <c r="J51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
-        <v>8</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E52" t="s">
-        <v>251</v>
-      </c>
-      <c r="F52" t="s">
-        <v>252</v>
-      </c>
-      <c r="G52" t="s">
+    </row>
+    <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="H52" t="s">
-        <v>134</v>
-      </c>
-      <c r="J52" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="64" x14ac:dyDescent="0.2">
-      <c r="A53" s="6">
-        <v>9</v>
-      </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" t="s">
-        <v>256</v>
-      </c>
-      <c r="F53" t="s">
-        <v>257</v>
-      </c>
-      <c r="G53" s="3">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="80" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="G54" s="11" t="s">
+      <c r="F61" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="H54" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I54" s="11" t="s">
+      <c r="G61" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="H61" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J61" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="B62" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="11" t="s">
+      <c r="F62" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="G62" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H62" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J62" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
+        <v>11</v>
+      </c>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="G55" t="s">
-        <v>216</v>
-      </c>
-      <c r="H55" t="s">
-        <v>80</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="D63" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B56" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C56" s="11" t="s">
+      <c r="E63" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="13" t="s">
+      <c r="F63" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="F56" s="13" t="s">
+      <c r="G63" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="G56" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H56" t="s">
-        <v>80</v>
-      </c>
-      <c r="I56" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>10</v>
-      </c>
-      <c r="C57" t="s">
-        <v>274</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="E57" t="s">
-        <v>274</v>
-      </c>
-      <c r="F57" t="s">
-        <v>276</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H63" t="s">
+        <v>117</v>
+      </c>
+      <c r="J63" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="11">
+        <v>13</v>
+      </c>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J57" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
+      <c r="D64" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="E64" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11" t="s">
+      <c r="F64" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="G64" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="H64" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
+        <v>14</v>
+      </c>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="H58" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I58" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="D65" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B59" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="F59" s="13" t="s">
+      <c r="E65" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="G59" s="13" t="s">
+      <c r="F65" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="H59" t="s">
-        <v>80</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="G65" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="B60" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" t="s">
-        <v>286</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="H65" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="11">
+        <v>15</v>
+      </c>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D66" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="G60" t="s">
+      <c r="E66" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="H60" t="s">
-        <v>80</v>
-      </c>
-      <c r="I60" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>11</v>
-      </c>
-      <c r="C61" s="4" t="s">
+      <c r="F66" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="G66" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="E61" t="s">
+      <c r="H66" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="F61" t="s">
+    </row>
+    <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="11">
+        <v>16</v>
+      </c>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="G61" t="s">
+      <c r="D67" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="H61" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="F67" s="13" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>12</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="G67" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="E62" t="s">
+      <c r="H67" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="11">
+        <v>17</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="F62" t="s">
+      <c r="D68" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E68" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="G62" t="s">
+      <c r="F68" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J62" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>13</v>
-      </c>
-      <c r="C63" s="4" t="s">
+      <c r="G68" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="H68" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="11">
+        <v>18</v>
+      </c>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="F63" t="s">
+      <c r="D69" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="G63" t="s">
+      <c r="E69" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="H63" t="s">
-        <v>134</v>
-      </c>
-      <c r="J63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="64" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>14</v>
-      </c>
-      <c r="C64" s="4" t="s">
+      <c r="F69" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>15</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>16</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="64" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>17</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>18</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
+      <c r="G69" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11">
         <v>19</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>335</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>75</v>
-      </c>
+      <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="E70" t="s">
-        <v>337</v>
-      </c>
-      <c r="F70" t="s">
-        <v>338</v>
-      </c>
-      <c r="G70" t="s">
-        <v>339</v>
-      </c>
-      <c r="H70" t="s">
-        <v>80</v>
-      </c>
-      <c r="I70" s="11" t="s">
-        <v>81</v>
+        <v>304</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="J70" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-    </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-    </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-    </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="13">
+        <v>20</v>
+      </c>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
+        <v>21</v>
+      </c>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="11">
+        <v>22</v>
+      </c>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="F74" s="11"/>
+      <c r="G74" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="13"/>
+    </row>
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F76" s="11"/>
+      <c r="G76" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D77" s="13"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4449,146 +4720,146 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="41.5" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="41.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="E3" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="G3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="E4" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="C6" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C6" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>359</v>
+        <v>199</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4601,22 +4872,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4626,26 +4897,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -4852,26 +5103,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226BE694-A00C-4E31-A532-690E39C51D9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4888,4 +5140,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/requirements/Procedure.xlsx
+++ b/input/requirements/Procedure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TessavanAlphen\Projects\GBB-IG\input\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahenket/Development/GitHub/Nictiz/GBB-IG/input/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E763DAFF-1EFF-401A-84AC-F527979C6F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20572DD5-0653-6B41-AC4F-00D5B12D1465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -216,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="403">
   <si>
     <t>Veld</t>
   </si>
@@ -1441,6 +1441,12 @@
   <si>
     <t>1..1
 Verplicht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De reden waarom de procedure is uitgevoerd of de indicatie van de verrichtign. </t>
+  </si>
+  <si>
+    <t>Dit kan een begrip uit een terminologie zijn of een verwijzing naar een specifieke instantie die de reden/indicatie beschrijft.</t>
   </si>
 </sst>
 </file>
@@ -2697,12 +2703,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="218.44140625" customWidth="1"/>
+    <col min="1" max="1" width="218.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
     </row>
   </sheetData>
@@ -2714,18 +2720,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="190.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="191" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="59.6640625" customWidth="1"/>
-    <col min="3" max="3" width="58.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="99.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="58.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="99.83203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="190.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="191" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2733,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2741,7 +2747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2749,7 +2755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2757,7 +2763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2765,7 +2771,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2773,7 +2779,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2792,7 +2798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -2803,7 +2809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>335</v>
       </c>
@@ -2821,20 +2827,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
   <dimension ref="A1:K77"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="22.44140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="4" customWidth="1"/>
+    <col min="1" max="2" width="22.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="17" style="4" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="68.44140625" customWidth="1"/>
-    <col min="7" max="7" width="52.109375" customWidth="1"/>
+    <col min="6" max="6" width="68.5" customWidth="1"/>
+    <col min="7" max="7" width="52.1640625" customWidth="1"/>
     <col min="8" max="9" width="48.6640625" customWidth="1"/>
-    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="10" max="10" width="34.5" customWidth="1"/>
     <col min="11" max="11" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2843,7 +2849,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>16</v>
       </c>
@@ -2876,7 +2882,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>0</v>
       </c>
@@ -2901,7 +2907,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -2924,7 +2930,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
@@ -2951,7 +2957,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>34</v>
       </c>
@@ -2978,7 +2984,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>38</v>
       </c>
@@ -3005,7 +3011,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>43</v>
       </c>
@@ -3030,7 +3036,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>48</v>
       </c>
@@ -3057,7 +3063,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>53</v>
       </c>
@@ -3084,7 +3090,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -3108,7 +3114,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>63</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>341</v>
       </c>
@@ -3167,7 +3173,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <v>2</v>
       </c>
@@ -3190,7 +3196,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>77</v>
       </c>
@@ -3213,7 +3219,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>80</v>
       </c>
@@ -3236,7 +3242,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>83</v>
       </c>
@@ -3259,7 +3265,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>3</v>
       </c>
@@ -3279,7 +3285,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>88</v>
       </c>
@@ -3306,7 +3312,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>94</v>
       </c>
@@ -3331,7 +3337,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>99</v>
       </c>
@@ -3358,7 +3364,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>104</v>
       </c>
@@ -3383,7 +3389,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A23" s="13">
         <v>4</v>
       </c>
@@ -3406,7 +3412,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>112</v>
       </c>
@@ -3433,7 +3439,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>118</v>
       </c>
@@ -3456,7 +3462,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>121</v>
       </c>
@@ -3479,7 +3485,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>124</v>
       </c>
@@ -3502,7 +3508,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>128</v>
       </c>
@@ -3525,7 +3531,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
         <v>132</v>
       </c>
@@ -3548,7 +3554,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
         <v>136</v>
       </c>
@@ -3571,7 +3577,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="13" t="s">
         <v>139</v>
       </c>
@@ -3594,7 +3600,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="13" t="s">
         <v>144</v>
       </c>
@@ -3617,7 +3623,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="13" t="s">
         <v>148</v>
       </c>
@@ -3640,7 +3646,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="13" t="s">
         <v>152</v>
       </c>
@@ -3663,7 +3669,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
         <v>156</v>
       </c>
@@ -3686,7 +3692,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="13" t="s">
         <v>160</v>
       </c>
@@ -3709,7 +3715,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="13" t="s">
         <v>164</v>
       </c>
@@ -3732,7 +3738,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>168</v>
       </c>
@@ -3755,7 +3761,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="13" t="s">
         <v>172</v>
       </c>
@@ -3778,7 +3784,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="13" t="s">
         <v>176</v>
       </c>
@@ -3801,7 +3807,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" s="13" t="s">
         <v>180</v>
       </c>
@@ -3824,7 +3830,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" s="13" t="s">
         <v>184</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
         <v>188</v>
       </c>
@@ -3870,7 +3876,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="13" t="s">
         <v>192</v>
       </c>
@@ -3897,7 +3903,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="13" t="s">
         <v>64</v>
@@ -3927,7 +3933,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="11"/>
       <c r="B46" s="13" t="s">
         <v>64</v>
@@ -3957,7 +3963,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="5" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="13">
         <v>5</v>
       </c>
@@ -3984,7 +3990,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
         <v>205</v>
       </c>
@@ -4010,7 +4016,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
         <v>209</v>
       </c>
@@ -4032,7 +4038,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="13">
         <v>6</v>
       </c>
@@ -4059,7 +4065,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>7</v>
       </c>
@@ -4069,12 +4075,20 @@
       <c r="E51" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="G51" s="11"/>
+      <c r="F51" t="s">
+        <v>401</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>390</v>
+      </c>
       <c r="J51" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
         <v>220</v>
       </c>
@@ -4101,7 +4115,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
         <v>225</v>
       </c>
@@ -4128,7 +4142,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="11">
         <v>8</v>
       </c>
@@ -4155,7 +4169,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="13">
         <v>9</v>
       </c>
@@ -4182,7 +4196,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="11" t="s">
         <v>239</v>
       </c>
@@ -4212,7 +4226,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="11" t="s">
         <v>244</v>
       </c>
@@ -4244,7 +4258,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
         <v>248</v>
       </c>
@@ -4274,7 +4288,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="11">
         <v>10</v>
       </c>
@@ -4301,7 +4315,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="13" t="s">
         <v>257</v>
       </c>
@@ -4329,7 +4343,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="11" t="s">
         <v>261</v>
       </c>
@@ -4357,7 +4371,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="11" t="s">
         <v>264</v>
       </c>
@@ -4385,7 +4399,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="11">
         <v>11</v>
       </c>
@@ -4412,7 +4426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A64" s="11">
         <v>13</v>
       </c>
@@ -4439,7 +4453,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" s="11">
         <v>14</v>
       </c>
@@ -4466,7 +4480,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="11">
         <v>15</v>
       </c>
@@ -4493,7 +4507,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="11">
         <v>16</v>
       </c>
@@ -4520,7 +4534,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A68" s="11">
         <v>17</v>
       </c>
@@ -4547,7 +4561,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A69" s="11">
         <v>18</v>
       </c>
@@ -4574,7 +4588,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="11">
         <v>19</v>
       </c>
@@ -4599,7 +4613,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
         <v>308</v>
       </c>
@@ -4626,7 +4640,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="13">
         <v>20</v>
       </c>
@@ -4647,7 +4661,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="11">
         <v>21</v>
       </c>
@@ -4668,7 +4682,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="11">
         <v>22</v>
       </c>
@@ -4690,7 +4704,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
       <c r="B75" s="13"/>
       <c r="C75" s="13"/>
@@ -4698,13 +4712,13 @@
       <c r="F75" s="11"/>
       <c r="G75" s="13"/>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F76" s="11"/>
       <c r="G76" s="13" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D77" s="13"/>
       <c r="F77" s="11"/>
       <c r="G77" s="11"/>
@@ -4720,18 +4734,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
     <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" customWidth="1"/>
-    <col min="7" max="7" width="41.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>313</v>
       </c>
@@ -4754,7 +4768,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>315</v>
       </c>
@@ -4777,7 +4791,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
         <v>274</v>
       </c>
@@ -4794,7 +4808,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
         <v>323</v>
       </c>
@@ -4811,7 +4825,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
         <v>326</v>
       </c>
@@ -4828,7 +4842,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="C6" s="7" t="s">
         <v>328</v>
       </c>
@@ -4845,7 +4859,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>329</v>
       </c>
@@ -4872,20 +4886,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>334</v>
       </c>
@@ -4897,6 +4911,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5103,7 +5128,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5112,18 +5137,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226BE694-A00C-4E31-A532-690E39C51D9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5142,21 +5173,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>